--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>482765</v>
+        <v>136997286</v>
       </c>
       <c r="B2" t="n">
-        <v>96708</v>
+        <v>101563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>222498</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bispbergs klack NR, Dlr</t>
+          <t>Bispbergsklack, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544989</v>
+        <v>544899</v>
       </c>
       <c r="R2" t="n">
-        <v>6691249</v>
+        <v>6691219</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-08-14</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-08-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>En tuva med diameter= 5cm, på stig</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,35 +773,734 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136997286</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>482765</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96708</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bispbergs klack NR, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>544989</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6691249</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2012-08-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2012-08-14</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>En tuva med diameter= 5cm, på stig</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/482765</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136997379</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bispbergsklack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>544977</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6691007</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136997379</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136997314</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bispbergsklack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>544930</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6691192</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136997314</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136997339</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bispbergsklack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>544985</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6691035</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136997339</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136997365</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bispbergsklack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>544977</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6691007</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136997365</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136997412</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101563</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bispbergsklack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>544966</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6690990</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136997412</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136997286</v>
       </c>
       <c r="B2" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>136997379</v>
       </c>
       <c r="B4" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136997314</v>
       </c>
       <c r="B5" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136997339</v>
       </c>
       <c r="B6" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136997365</v>
       </c>
       <c r="B7" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>136997412</v>
       </c>
       <c r="B8" t="n">
-        <v>101563</v>
+        <v>101569</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136997286</v>
       </c>
       <c r="B2" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -912,7 +912,7 @@
         <v>136997379</v>
       </c>
       <c r="B4" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>136997314</v>
       </c>
       <c r="B5" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1146,7 +1146,7 @@
         <v>136997339</v>
       </c>
       <c r="B6" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>136997365</v>
       </c>
       <c r="B7" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>136997412</v>
       </c>
       <c r="B8" t="n">
-        <v>101569</v>
+        <v>101571</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136997286</v>
+        <v>137102979</v>
       </c>
       <c r="B2" t="n">
-        <v>101571</v>
+        <v>96574</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>2812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bispbergsklack, Dlr</t>
+          <t>Bispbergs klack, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544899</v>
+        <v>544877</v>
       </c>
       <c r="R2" t="n">
-        <v>6691219</v>
+        <v>6691356</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,22 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -773,34 +759,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136997286</t>
+          <t>https://artportalen.se/Sighting/137102979</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>482765</v>
+        <v>137102761</v>
       </c>
       <c r="B3" t="n">
-        <v>96708</v>
+        <v>5182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bispbergs klack NR, Dlr</t>
+          <t>Bispbergs klack, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544989</v>
+        <v>544877</v>
       </c>
       <c r="R3" t="n">
-        <v>6691249</v>
+        <v>6691356</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,17 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-08-14</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-08-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>En tuva med diameter= 5cm, på stig</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,58 +868,53 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/482765</t>
+          <t>https://artportalen.se/Sighting/137102761</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136997379</v>
+        <v>136997286</v>
       </c>
       <c r="B4" t="n">
-        <v>99361</v>
+        <v>101572</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -948,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544977</v>
+        <v>544899</v>
       </c>
       <c r="R4" t="n">
-        <v>6691007</v>
+        <v>6691219</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1020,16 +1000,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136997379</t>
+          <t>https://artportalen.se/Sighting/136997286</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136997314</v>
+        <v>137102710</v>
       </c>
       <c r="B5" t="n">
-        <v>101571</v>
+        <v>101572</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1055,23 +1035,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bispbergsklack, Dlr</t>
+          <t>Bispbergs klack, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544930</v>
+        <v>544853</v>
       </c>
       <c r="R5" t="n">
-        <v>6691192</v>
+        <v>6691365</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,22 +1071,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,34 +1085,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136997314</t>
+          <t>https://artportalen.se/Sighting/137102710</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136997339</v>
+        <v>482765</v>
       </c>
       <c r="B6" t="n">
-        <v>101571</v>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1154,41 +1119,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bispbergsklack, Dlr</t>
+          <t>Bispbergs klack NR, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544985</v>
+        <v>544989</v>
       </c>
       <c r="R6" t="n">
-        <v>6691035</v>
+        <v>6691249</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,22 +1173,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2012-08-14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2012-08-14</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>En tuva med diameter= 5cm, på stig</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,34 +1192,38 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136997339</t>
+          <t>https://artportalen.se/Sighting/482765</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136997365</v>
+        <v>137103507</v>
       </c>
       <c r="B7" t="n">
-        <v>101571</v>
+        <v>58005</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,41 +1231,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bispbergsklack, Dlr</t>
+          <t>Bispbergs klack, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
         <v>544977</v>
       </c>
       <c r="R7" t="n">
-        <v>6691007</v>
+        <v>6691002</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1329,22 +1290,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,56 +1304,55 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Stig-Åke Svenson</t>
+          <t>Patric Engfeldt</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136997365</t>
+          <t>https://artportalen.se/Sighting/137103507</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136997412</v>
+        <v>136997379</v>
       </c>
       <c r="B8" t="n">
-        <v>101571</v>
+        <v>99362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1416,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544966</v>
+        <v>544977</v>
       </c>
       <c r="R8" t="n">
-        <v>6690990</v>
+        <v>6691007</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1488,7 +1438,577 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136997379</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136997314</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101572</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bispbergsklack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>544930</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6691192</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136997314</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136997339</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101572</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bispbergsklack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>544985</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6691035</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136997339</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136997365</v>
+      </c>
+      <c r="B11" t="n">
+        <v>101572</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bispbergsklack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>544977</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6691007</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136997365</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136997412</v>
+      </c>
+      <c r="B12" t="n">
+        <v>101572</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bispbergsklack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>544966</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6690990</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Stig-Åke Svenson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136997412</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137103473</v>
+      </c>
+      <c r="B13" t="n">
+        <v>101572</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Griggersklack, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>544981</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6691031</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patric Engfeldt</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137103473</t>
         </is>
       </c>
     </row>
@@ -1501,6 +2021,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137102979</v>
       </c>
       <c r="B2" t="n">
-        <v>96574</v>
+        <v>96580</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136997286</v>
       </c>
       <c r="B4" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>137102710</v>
       </c>
       <c r="B5" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>136997379</v>
       </c>
       <c r="B8" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136997314</v>
       </c>
       <c r="B9" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136997339</v>
       </c>
       <c r="B10" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136997365</v>
       </c>
       <c r="B11" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136997412</v>
       </c>
       <c r="B12" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137103473</v>
       </c>
       <c r="B13" t="n">
-        <v>101572</v>
+        <v>101578</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137102979</v>
       </c>
       <c r="B2" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136997286</v>
       </c>
       <c r="B4" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>137102710</v>
       </c>
       <c r="B5" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>136997379</v>
       </c>
       <c r="B8" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136997314</v>
       </c>
       <c r="B9" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136997339</v>
       </c>
       <c r="B10" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136997365</v>
       </c>
       <c r="B11" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136997412</v>
       </c>
       <c r="B12" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137103473</v>
       </c>
       <c r="B13" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137102979</v>
       </c>
       <c r="B2" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136997286</v>
       </c>
       <c r="B4" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>137102710</v>
       </c>
       <c r="B5" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>136997379</v>
       </c>
       <c r="B8" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136997314</v>
       </c>
       <c r="B9" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136997339</v>
       </c>
       <c r="B10" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136997365</v>
       </c>
       <c r="B11" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136997412</v>
       </c>
       <c r="B12" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137103473</v>
       </c>
       <c r="B13" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137102979</v>
       </c>
       <c r="B2" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136997286</v>
       </c>
       <c r="B4" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>137102710</v>
       </c>
       <c r="B5" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>136997379</v>
       </c>
       <c r="B8" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136997314</v>
       </c>
       <c r="B9" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136997339</v>
       </c>
       <c r="B10" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136997365</v>
       </c>
       <c r="B11" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136997412</v>
       </c>
       <c r="B12" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137103473</v>
       </c>
       <c r="B13" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137102979</v>
       </c>
       <c r="B2" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136997286</v>
       </c>
       <c r="B4" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>137102710</v>
       </c>
       <c r="B5" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>137103507</v>
       </c>
       <c r="B7" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>136997379</v>
       </c>
       <c r="B8" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136997314</v>
       </c>
       <c r="B9" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136997339</v>
       </c>
       <c r="B10" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136997365</v>
       </c>
       <c r="B11" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136997412</v>
       </c>
       <c r="B12" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137103473</v>
       </c>
       <c r="B13" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137102979</v>
       </c>
       <c r="B2" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         <v>136997286</v>
       </c>
       <c r="B4" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>137102710</v>
       </c>
       <c r="B5" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>137103507</v>
       </c>
       <c r="B7" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>136997379</v>
       </c>
       <c r="B8" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1447,7 +1447,7 @@
         <v>136997314</v>
       </c>
       <c r="B9" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>136997339</v>
       </c>
       <c r="B10" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         <v>136997365</v>
       </c>
       <c r="B11" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>136997412</v>
       </c>
       <c r="B12" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137103473</v>
       </c>
       <c r="B13" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -811,11 +811,7 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bispbergs klack, Dlr</t>
@@ -1249,11 +1245,7 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bispbergs klack, Dlr</t>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137102979</v>
       </c>
       <c r="B2" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>136997286</v>
       </c>
       <c r="B4" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137102710</v>
       </c>
       <c r="B5" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136997379</v>
       </c>
       <c r="B8" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>136997314</v>
       </c>
       <c r="B9" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>136997339</v>
       </c>
       <c r="B10" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136997365</v>
       </c>
       <c r="B11" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>136997412</v>
       </c>
       <c r="B12" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137103473</v>
       </c>
       <c r="B13" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137102979</v>
       </c>
       <c r="B2" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137102761</v>
       </c>
       <c r="B3" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>136997286</v>
       </c>
       <c r="B4" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137102710</v>
       </c>
       <c r="B5" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137103507</v>
       </c>
       <c r="B7" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136997379</v>
       </c>
       <c r="B8" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>136997314</v>
       </c>
       <c r="B9" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>136997339</v>
       </c>
       <c r="B10" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136997365</v>
       </c>
       <c r="B11" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>136997412</v>
       </c>
       <c r="B12" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137103473</v>
       </c>
       <c r="B13" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137102979</v>
       </c>
       <c r="B2" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>136997286</v>
       </c>
       <c r="B4" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137102710</v>
       </c>
       <c r="B5" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136997379</v>
       </c>
       <c r="B8" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>136997314</v>
       </c>
       <c r="B9" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>136997339</v>
       </c>
       <c r="B10" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136997365</v>
       </c>
       <c r="B11" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>136997412</v>
       </c>
       <c r="B12" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137103473</v>
       </c>
       <c r="B13" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137102979</v>
       </c>
       <c r="B2" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>136997286</v>
       </c>
       <c r="B4" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137102710</v>
       </c>
       <c r="B5" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137103507</v>
       </c>
       <c r="B7" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136997379</v>
       </c>
       <c r="B8" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>136997314</v>
       </c>
       <c r="B9" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>136997339</v>
       </c>
       <c r="B10" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136997365</v>
       </c>
       <c r="B11" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>136997412</v>
       </c>
       <c r="B12" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137103473</v>
       </c>
       <c r="B13" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137102979</v>
       </c>
       <c r="B2" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>136997286</v>
       </c>
       <c r="B4" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137102710</v>
       </c>
       <c r="B5" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136997379</v>
       </c>
       <c r="B8" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>136997314</v>
       </c>
       <c r="B9" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>136997339</v>
       </c>
       <c r="B10" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136997365</v>
       </c>
       <c r="B11" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>136997412</v>
       </c>
       <c r="B12" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137103473</v>
       </c>
       <c r="B13" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137102979</v>
       </c>
       <c r="B2" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>136997286</v>
       </c>
       <c r="B4" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137102710</v>
       </c>
       <c r="B5" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137103507</v>
       </c>
       <c r="B7" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136997379</v>
       </c>
       <c r="B8" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>136997314</v>
       </c>
       <c r="B9" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>136997339</v>
       </c>
       <c r="B10" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136997365</v>
       </c>
       <c r="B11" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>136997412</v>
       </c>
       <c r="B12" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137103473</v>
       </c>
       <c r="B13" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137102979</v>
       </c>
       <c r="B2" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>136997286</v>
       </c>
       <c r="B4" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137102710</v>
       </c>
       <c r="B5" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136997379</v>
       </c>
       <c r="B8" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>136997314</v>
       </c>
       <c r="B9" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>136997339</v>
       </c>
       <c r="B10" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136997365</v>
       </c>
       <c r="B11" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>136997412</v>
       </c>
       <c r="B12" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137103473</v>
       </c>
       <c r="B13" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137102979</v>
       </c>
       <c r="B2" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>136997286</v>
       </c>
       <c r="B4" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137102710</v>
       </c>
       <c r="B5" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136997379</v>
       </c>
       <c r="B8" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>136997314</v>
       </c>
       <c r="B9" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>136997339</v>
       </c>
       <c r="B10" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136997365</v>
       </c>
       <c r="B11" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>136997412</v>
       </c>
       <c r="B12" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137103473</v>
       </c>
       <c r="B13" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137102979</v>
       </c>
       <c r="B2" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>136997286</v>
       </c>
       <c r="B4" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137102710</v>
       </c>
       <c r="B5" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136997379</v>
       </c>
       <c r="B8" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>136997314</v>
       </c>
       <c r="B9" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>136997339</v>
       </c>
       <c r="B10" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136997365</v>
       </c>
       <c r="B11" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>136997412</v>
       </c>
       <c r="B12" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137103473</v>
       </c>
       <c r="B13" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -888,7 +888,7 @@
         <v>136997286</v>
       </c>
       <c r="B4" t="n">
-        <v>101650</v>
+        <v>101651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136997379</v>
       </c>
       <c r="B8" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>136997314</v>
       </c>
       <c r="B9" t="n">
-        <v>101650</v>
+        <v>101651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>136997339</v>
       </c>
       <c r="B10" t="n">
-        <v>101650</v>
+        <v>101651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136997365</v>
       </c>
       <c r="B11" t="n">
-        <v>101650</v>
+        <v>101651</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>136997412</v>
       </c>
       <c r="B12" t="n">
-        <v>101650</v>
+        <v>101651</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 38692-2026 artfynd.xlsx
+++ b/artfynd/A 38692-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137102979</v>
       </c>
       <c r="B2" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>136997286</v>
       </c>
       <c r="B4" t="n">
-        <v>101651</v>
+        <v>101654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,7 +1005,7 @@
         <v>137102710</v>
       </c>
       <c r="B5" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>137103507</v>
       </c>
       <c r="B7" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
         <v>136997379</v>
       </c>
       <c r="B8" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>136997314</v>
       </c>
       <c r="B9" t="n">
-        <v>101651</v>
+        <v>101654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>136997339</v>
       </c>
       <c r="B10" t="n">
-        <v>101651</v>
+        <v>101654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>136997365</v>
       </c>
       <c r="B11" t="n">
-        <v>101651</v>
+        <v>101654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>136997412</v>
       </c>
       <c r="B12" t="n">
-        <v>101651</v>
+        <v>101654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137103473</v>
       </c>
       <c r="B13" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
